--- a/Projects/Downtown Riverside Metro Link/03 - Scope & Pricing/Riverside MetroLink - Scope Worksheet.xlsx
+++ b/Projects/Downtown Riverside Metro Link/03 - Scope & Pricing/Riverside MetroLink - Scope Worksheet.xlsx
@@ -820,7 +820,7 @@
       </c>
       <c r="K10" s="28" t="inlineStr">
         <is>
-          <t>Branded 'Holiday Express' pole banners — one-time purchase; customer-owned, designed in-house.</t>
+          <t>24″×48″ branded 'Holiday Express' pole banners — 18 oz vinyl, double-sided, hemmed + grommeted (customer-owned)</t>
         </is>
       </c>
       <c r="L10" s="28" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="K11" s="28" t="inlineStr">
         <is>
-          <t>Powder-coated steel pole banner brackets — one-time purchase; customer-owned, reusable indefinitely.</t>
+          <t>Heavy-duty powder-coated steel pole banner brackets — top + bottom arm pair, stainless banding mount (no drilling, customer-owned)</t>
         </is>
       </c>
       <c r="L11" s="28" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K12" s="28" t="inlineStr">
         <is>
-          <t>Annual install of pole banner program at season open; removal at season close. Storage between seasons included.</t>
+          <t>Annual install + removal of 35 pole banners — bucket-truck access, off-season storage included</t>
         </is>
       </c>
       <c r="L12" s="28" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="K13" s="28" t="inlineStr">
         <is>
-          <t>Warm-white string lighting on the eaves of all 16 platform canopies — 1,024 lineal feet of evening glow across the platforms.</t>
+          <t>Commercial-grade C9 LED warm-white string lighting on 16 platform canopies — 1,024 LF on the eaves</t>
         </is>
       </c>
       <c r="L13" s="28" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="K14" s="28" t="inlineStr">
         <is>
-          <t>Warm-white string lighting on the bus stop waiting canopies — additional warm-white evening accent at the perimeter.</t>
+          <t>Commercial-grade C9 LED warm-white string lighting on 2 bus-stop waiting canopies — 234 LF on the eaves</t>
         </is>
       </c>
       <c r="L14" s="28" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="K15" s="28" t="inlineStr">
         <is>
-          <t>Lit evergreen garland swagged across the perimeter fence — 621 lineal feet of warm-white glow framing the property edge.</t>
+          <t>14″ PVC pine garland with warm-white mini-LED lights — 621 LF on the perimeter fence</t>
         </is>
       </c>
       <c r="L15" s="28" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="K16" s="28" t="inlineStr">
         <is>
-          <t>Lit evergreen garland on the building eave — warm-white evening accent that reads from the platforms.</t>
+          <t>14″ PVC pine garland with warm-white mini-LED lights — 144 LF on the building eave</t>
         </is>
       </c>
       <c r="L16" s="28" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="K17" s="28" t="inlineStr">
         <is>
-          <t>Lit evergreen garland on the center driveway gates — the welcome gesture as guests enter the station.</t>
+          <t>14″ PVC pine garland with warm-white mini-LED lights — 261 LF on the center driveway gates</t>
         </is>
       </c>
       <c r="L17" s="28" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="K18" s="28" t="inlineStr">
         <is>
-          <t>Custom-fabricated 5 ft lighted wreaths between the four entrance brick columns — the threshold gesture of the program.</t>
+          <t>5 ft pre-lit warm-white LED commercial wreaths with red, green &amp; gold ornament clusters — 4 between the entrance brick columns</t>
         </is>
       </c>
       <c r="L18" s="28" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="K19" s="28" t="inlineStr">
         <is>
-          <t>Oversized 10 ft lighted wreath on the stair tower — a feature element visible from a block away.</t>
+          <t>10 ft oversized pre-lit warm-white LED commercial wreath with red, green &amp; gold ornament clusters — mounted on the stair-tower brick column</t>
         </is>
       </c>
       <c r="L19" s="28" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="K20" s="28" t="inlineStr">
         <is>
-          <t>18 ft traditional Christmas tree at the centerpiece location — pre-lit warm white with red, green, and gold ornaments.</t>
+          <t>18 ft pre-lit artificial steel-frame Christmas tree — warm-white LED with red, green &amp; gold ornaments, 2 ft LED star topper</t>
         </is>
       </c>
       <c r="L20" s="28" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="K21" s="28" t="inlineStr">
         <is>
-          <t>Walk-through warm-white lighted ornament archway at the bus loading island — a photo moment and the visual anchor of the program.</t>
+          <t>12 ft warm-white LED walk-through ornament archway with companion ornament — steel armature, ground-anchored at bus loading island</t>
         </is>
       </c>
       <c r="L21" s="28" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="K26" s="28" t="inlineStr">
         <is>
-          <t>Lighted snowflakes along the bridge and platform railings — additional warm-white evening accents.</t>
+          <t>30″ aluminum-frame warm-white rope-light snowflakes — 12 fixtures railing-mounted along bridge and platforms</t>
         </is>
       </c>
       <c r="L26" s="28" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="K27" s="28" t="inlineStr">
         <is>
-          <t>Walk-through lighted gift box archway with red bow — additional photo moment and high social-media value installation.</t>
+          <t>12 ft lighted walk-through gift box archway with red bow — steel frame, LED + PVC mesh, ground-anchored</t>
         </is>
       </c>
       <c r="L27" s="28" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="K28" s="28" t="inlineStr">
         <is>
-          <t>Custom 'City of Riverside' lighted bell display — Mission Inn-style, branded for the City. One-time custom fabrication, customer-owned.</t>
+          <t>10 ft custom-fabricated Mission Inn-style 'City of Riverside' lighted bell display — steel armature, warm-white LED + rope light, PVC mesh, branded acrylic base (customer-owned)</t>
         </is>
       </c>
       <c r="L28" s="28" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="K29" s="28" t="inlineStr">
         <is>
-          <t>Annual install and removal of the City of Riverside Bell Display each season.</t>
+          <t>Annual install + removal of the City of Riverside Bell Display — positioning, anchoring, electrical tie-in</t>
         </is>
       </c>
       <c r="L29" s="28" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="K30" s="28" t="inlineStr">
         <is>
-          <t>Off-season climate-controlled storage of the customer-owned Bell Display.</t>
+          <t>Off-season climate-controlled crated storage of the City of Riverside Bell Display</t>
         </is>
       </c>
       <c r="L30" s="28" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="K31" s="28" t="inlineStr">
         <is>
-          <t>21 ft red-and-green LED spiral tree with gold star topper — the Signature-tier alternative to the Traditional centerpiece tree.</t>
+          <t>21 ft steel-frame red-and-green LED spiral tree with gold star topper — alternating LED spiral wraps, warm-white rope light, PVC mesh (Signature alt. to Traditional centerpiece)</t>
         </is>
       </c>
       <c r="L31" s="28" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="K32" s="28" t="inlineStr">
         <is>
-          <t>Stacked oversized lighted gift box pyramid — 12 ft tall, additional photo moment at a separate plaza location.</t>
+          <t>12 ft stacked lighted gift box tower — multiple aluminum-frame boxes with red, green &amp; white LED net wrap, ground-anchored at second plaza location</t>
         </is>
       </c>
       <c r="L32" s="28" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="K33" s="28" t="inlineStr">
         <is>
-          <t>Decorated garland upgrade — adds red, green &amp; gold ornament clusters and bows to the perimeter fence garland.</t>
+          <t>Decorated upgrade — red, green &amp; gold ornament clusters and bows on the 621 LF perimeter fence garland</t>
         </is>
       </c>
       <c r="L33" s="28" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="K34" s="28" t="inlineStr">
         <is>
-          <t>Decorated garland upgrade — adds red, green &amp; gold ornament clusters and bows to the building eave garland.</t>
+          <t>Decorated upgrade — red, green &amp; gold ornament clusters and bows on the 144 LF building eave garland</t>
         </is>
       </c>
       <c r="L34" s="28" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="K35" s="28" t="inlineStr">
         <is>
-          <t>Decorated garland upgrade — adds red, green &amp; gold ornament clusters and bows to the center driveway gate garland.</t>
+          <t>Decorated upgrade — red, green &amp; gold ornament clusters and bows on the 261 LF center driveway garland</t>
         </is>
       </c>
       <c r="L35" s="28" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="K36" s="28" t="inlineStr">
         <is>
-          <t>Illuminated 'Happy Holidays' overhead marquee with skyline silhouette — custom-fabricated signage element.</t>
+          <t>12 ft wide custom-fabricated illuminated 'Happy Holidays' overhead marquee with skyline silhouette — PVC mesh, warm-white channel-letter LED + rope light, span-mounted between columns</t>
         </is>
       </c>
       <c r="L36" s="28" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="K37" s="28" t="inlineStr">
         <is>
-          <t>Lit evergreen garland on the staircase tower and railing — warm-white evening accent on the vertical stair-tower feature.</t>
+          <t>14″ PVC pine garland with warm-white mini-LED lights — 207 LF on the staircase tower and railing</t>
         </is>
       </c>
       <c r="L37" s="28" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="K38" s="28" t="inlineStr">
         <is>
-          <t>Decorated garland upgrade — adds red, green &amp; gold ornament clusters and bows to the staircase tower garland.</t>
+          <t>Decorated upgrade — red, green &amp; gold ornament clusters and bows on the 207 LF staircase tower garland</t>
         </is>
       </c>
       <c r="L38" s="28" t="inlineStr">

--- a/Projects/Downtown Riverside Metro Link/03 - Scope & Pricing/Riverside MetroLink - Scope Worksheet.xlsx
+++ b/Projects/Downtown Riverside Metro Link/03 - Scope & Pricing/Riverside MetroLink - Scope Worksheet.xlsx
@@ -674,7 +674,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="21.75" customHeight="1" s="29">
       <c r="A4" s="32" t="inlineStr">
         <is>
@@ -699,7 +698,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8" ht="21.75" customHeight="1" s="29">
       <c r="A8" s="32" t="inlineStr">
         <is>
@@ -820,7 +818,7 @@
       </c>
       <c r="K10" s="28" t="inlineStr">
         <is>
-          <t>24″×48″ branded 'Holiday Express' pole banners — 18 oz vinyl, double-sided, hemmed + grommeted (customer-owned)</t>
+          <t>24″×48″ branded 'Holiday Express' pole banners (35) in 18 oz vinyl, double-sided, hemmed + grommeted (customer-owned)</t>
         </is>
       </c>
       <c r="L10" s="28" t="inlineStr">
@@ -879,7 +877,7 @@
       </c>
       <c r="K11" s="28" t="inlineStr">
         <is>
-          <t>Heavy-duty powder-coated steel pole banner brackets — top + bottom arm pair, stainless banding mount (no drilling, customer-owned)</t>
+          <t>Heavy-duty powder-coated steel pole banner brackets, top + bottom arm pair, stainless banding mount (no drilling, customer-owned)</t>
         </is>
       </c>
       <c r="L11" s="28" t="inlineStr">
@@ -938,7 +936,7 @@
       </c>
       <c r="K12" s="28" t="inlineStr">
         <is>
-          <t>Annual install + removal of 35 pole banners — bucket-truck access, off-season storage included</t>
+          <t>Annual install + removal of 35 pole banners, bucket-truck access, off-season storage included</t>
         </is>
       </c>
       <c r="L12" s="28" t="inlineStr">
@@ -997,7 +995,7 @@
       </c>
       <c r="K13" s="28" t="inlineStr">
         <is>
-          <t>Commercial-grade C9 LED warm-white string lighting on 16 platform canopies — 1,024 LF on the eaves</t>
+          <t>Commercial-grade C9 LED warm-white string lighting on 16 platform canopies, 1,024 LF on the eaves</t>
         </is>
       </c>
       <c r="L13" s="28" t="inlineStr">
@@ -1056,7 +1054,7 @@
       </c>
       <c r="K14" s="28" t="inlineStr">
         <is>
-          <t>Commercial-grade C9 LED warm-white string lighting on 2 bus-stop waiting canopies — 234 LF on the eaves</t>
+          <t>Commercial-grade C9 LED warm-white string lighting on 2 bus-stop waiting canopies, 234 LF on the eaves</t>
         </is>
       </c>
       <c r="L14" s="28" t="inlineStr">
@@ -1115,7 +1113,7 @@
       </c>
       <c r="K15" s="28" t="inlineStr">
         <is>
-          <t>14″ PVC pine garland with warm-white mini-LED lights — 621 LF on the perimeter fence</t>
+          <t>14″ PVC pine garland with warm-white mini-LED lights, 621 LF on the perimeter fence</t>
         </is>
       </c>
       <c r="L15" s="28" t="inlineStr">
@@ -1174,7 +1172,7 @@
       </c>
       <c r="K16" s="28" t="inlineStr">
         <is>
-          <t>14″ PVC pine garland with warm-white mini-LED lights — 144 LF on the building eave</t>
+          <t>14″ PVC pine garland with warm-white mini-LED lights, 144 LF on the building eave</t>
         </is>
       </c>
       <c r="L16" s="28" t="inlineStr">
@@ -1233,7 +1231,7 @@
       </c>
       <c r="K17" s="28" t="inlineStr">
         <is>
-          <t>14″ PVC pine garland with warm-white mini-LED lights — 261 LF on the center driveway gates</t>
+          <t>14″ PVC pine garland with warm-white mini-LED lights, 261 LF on the center driveway gates</t>
         </is>
       </c>
       <c r="L17" s="28" t="inlineStr">
@@ -1292,7 +1290,7 @@
       </c>
       <c r="K18" s="28" t="inlineStr">
         <is>
-          <t>5 ft pre-lit warm-white LED commercial wreaths with red, green &amp; gold ornament clusters — 4 between the entrance brick columns</t>
+          <t>5 ft pre-lit warm-white LED commercial wreaths with red, green &amp; gold ornament clusters, set of 4 between the entrance brick columns</t>
         </is>
       </c>
       <c r="L18" s="28" t="inlineStr">
@@ -1351,7 +1349,7 @@
       </c>
       <c r="K19" s="28" t="inlineStr">
         <is>
-          <t>10 ft oversized pre-lit warm-white LED commercial wreath with red, green &amp; gold ornament clusters — mounted on the stair-tower brick column</t>
+          <t>10 ft oversized pre-lit warm-white LED commercial wreath with red, green &amp; gold ornament clusters, mounted on the stair-tower brick column</t>
         </is>
       </c>
       <c r="L19" s="28" t="inlineStr">
@@ -1410,7 +1408,7 @@
       </c>
       <c r="K20" s="28" t="inlineStr">
         <is>
-          <t>18 ft pre-lit artificial steel-frame Christmas tree — warm-white LED with red, green &amp; gold ornaments, 2 ft LED star topper</t>
+          <t>18 ft pre-lit artificial steel-frame Christmas tree, warm-white LED with red, green &amp; gold ornaments, 2 ft LED star topper</t>
         </is>
       </c>
       <c r="L20" s="28" t="inlineStr">
@@ -1469,7 +1467,7 @@
       </c>
       <c r="K21" s="28" t="inlineStr">
         <is>
-          <t>12 ft warm-white LED walk-through ornament archway with companion ornament — steel armature, ground-anchored at bus loading island</t>
+          <t>12 ft warm-white LED walk-through ornament archway with companion ornament, steel armature, ground-anchored at bus loading island</t>
         </is>
       </c>
       <c r="L21" s="28" t="inlineStr">
@@ -1501,7 +1499,6 @@
       <c r="I22" s="45" t="n"/>
       <c r="J22" s="45" t="n"/>
     </row>
-    <row r="23"/>
     <row r="24" ht="21.75" customHeight="1" s="29">
       <c r="A24" s="48" t="inlineStr">
         <is>
@@ -1624,12 +1621,12 @@
       </c>
       <c r="K26" s="28" t="inlineStr">
         <is>
-          <t>30″ aluminum-frame warm-white rope-light snowflakes — 12 fixtures railing-mounted along bridge and platforms</t>
+          <t>30″ aluminum-frame warm-white rope-light snowflakes (12 fixtures), railing-mounted along bridge and platforms</t>
         </is>
       </c>
       <c r="L26" s="28" t="inlineStr">
         <is>
-          <t>Signature Add-Ons</t>
+          <t>Lighted Snowflakes</t>
         </is>
       </c>
       <c r="M26" s="28" t="inlineStr">
@@ -1685,7 +1682,7 @@
       </c>
       <c r="K27" s="28" t="inlineStr">
         <is>
-          <t>12 ft lighted walk-through gift box archway with red bow — steel frame, LED + PVC mesh, ground-anchored</t>
+          <t>12 ft lighted walk-through gift box archway with red bow, steel frame, LED + PVC mesh, ground-anchored</t>
         </is>
       </c>
       <c r="L27" s="28" t="inlineStr">
@@ -1746,12 +1743,12 @@
       </c>
       <c r="K28" s="28" t="inlineStr">
         <is>
-          <t>10 ft custom-fabricated Mission Inn-style 'City of Riverside' lighted bell display — steel armature, warm-white LED + rope light, PVC mesh, branded acrylic base (customer-owned)</t>
+          <t>10 ft custom-fabricated Mission Inn-style 'City of Riverside' lighted bell display, steel armature, warm-white LED + rope light, PVC mesh, branded acrylic base (customer-owned)</t>
         </is>
       </c>
       <c r="L28" s="28" t="inlineStr">
         <is>
-          <t>Signature Add-Ons</t>
+          <t>City of Riverside Bell Display</t>
         </is>
       </c>
       <c r="M28" s="28" t="inlineStr">
@@ -1807,12 +1804,12 @@
       </c>
       <c r="K29" s="28" t="inlineStr">
         <is>
-          <t>Annual install + removal of the City of Riverside Bell Display — positioning, anchoring, electrical tie-in</t>
+          <t>Annual install + removal of the City of Riverside Bell Display, positioning, anchoring, electrical tie-in</t>
         </is>
       </c>
       <c r="L29" s="28" t="inlineStr">
         <is>
-          <t>Signature Add-Ons</t>
+          <t>City of Riverside Bell Display</t>
         </is>
       </c>
       <c r="M29" s="28" t="inlineStr">
@@ -1873,7 +1870,7 @@
       </c>
       <c r="L30" s="28" t="inlineStr">
         <is>
-          <t>Signature Add-Ons</t>
+          <t>City of Riverside Bell Display</t>
         </is>
       </c>
       <c r="M30" s="28" t="inlineStr">
@@ -1929,7 +1926,7 @@
       </c>
       <c r="K31" s="28" t="inlineStr">
         <is>
-          <t>21 ft steel-frame red-and-green LED spiral tree with gold star topper — alternating LED spiral wraps, warm-white rope light, PVC mesh (Signature alt. to Traditional centerpiece)</t>
+          <t>21 ft steel-frame red-and-green LED spiral tree with gold star topper, alternating LED spiral wraps, warm-white rope light, PVC mesh (Signature alt. to Traditional centerpiece)</t>
         </is>
       </c>
       <c r="L31" s="28" t="inlineStr">
@@ -1990,12 +1987,12 @@
       </c>
       <c r="K32" s="28" t="inlineStr">
         <is>
-          <t>12 ft stacked lighted gift box tower — multiple aluminum-frame boxes with red, green &amp; white LED net wrap, ground-anchored at second plaza location</t>
+          <t>12 ft stacked lighted gift box tower, multiple aluminum-frame boxes with red, green &amp; white LED net wrap, ground-anchored at second plaza location</t>
         </is>
       </c>
       <c r="L32" s="28" t="inlineStr">
         <is>
-          <t>Signature Add-Ons</t>
+          <t>Gift Box Tower</t>
         </is>
       </c>
       <c r="M32" s="28" t="inlineStr">
@@ -2051,7 +2048,7 @@
       </c>
       <c r="K33" s="28" t="inlineStr">
         <is>
-          <t>Decorated upgrade — red, green &amp; gold ornament clusters and bows on the 621 LF perimeter fence garland</t>
+          <t>Decorated upgrade with red, green &amp; gold ornament clusters and bows on the 621 LF perimeter fence garland</t>
         </is>
       </c>
       <c r="L33" s="28" t="inlineStr">
@@ -2112,7 +2109,7 @@
       </c>
       <c r="K34" s="28" t="inlineStr">
         <is>
-          <t>Decorated upgrade — red, green &amp; gold ornament clusters and bows on the 144 LF building eave garland</t>
+          <t>Decorated upgrade with red, green &amp; gold ornament clusters and bows on the 144 LF building eave garland</t>
         </is>
       </c>
       <c r="L34" s="28" t="inlineStr">
@@ -2173,7 +2170,7 @@
       </c>
       <c r="K35" s="28" t="inlineStr">
         <is>
-          <t>Decorated upgrade — red, green &amp; gold ornament clusters and bows on the 261 LF center driveway garland</t>
+          <t>Decorated upgrade with red, green &amp; gold ornament clusters and bows on the 261 LF center driveway garland</t>
         </is>
       </c>
       <c r="L35" s="28" t="inlineStr">
@@ -2234,7 +2231,7 @@
       </c>
       <c r="K36" s="28" t="inlineStr">
         <is>
-          <t>12 ft wide custom-fabricated illuminated 'Happy Holidays' overhead marquee with skyline silhouette — PVC mesh, warm-white channel-letter LED + rope light, span-mounted between columns</t>
+          <t>12 ft wide custom-fabricated illuminated 'Happy Holidays' overhead marquee with skyline silhouette, PVC mesh, warm-white channel-letter LED + rope light, span-mounted between columns</t>
         </is>
       </c>
       <c r="L36" s="28" t="inlineStr">
@@ -2295,7 +2292,7 @@
       </c>
       <c r="K37" s="28" t="inlineStr">
         <is>
-          <t>14″ PVC pine garland with warm-white mini-LED lights — 207 LF on the staircase tower and railing</t>
+          <t>14″ PVC pine garland with warm-white mini-LED lights, 207 LF on the staircase tower and railing</t>
         </is>
       </c>
       <c r="L37" s="28" t="inlineStr">
@@ -2356,7 +2353,7 @@
       </c>
       <c r="K38" s="28" t="inlineStr">
         <is>
-          <t>Decorated upgrade — red, green &amp; gold ornament clusters and bows on the 207 LF staircase tower garland</t>
+          <t>Decorated upgrade with red, green &amp; gold ornament clusters and bows on the 207 LF staircase tower garland</t>
         </is>
       </c>
       <c r="L38" s="28" t="inlineStr">
@@ -2388,7 +2385,6 @@
       <c r="I39" s="45" t="n"/>
       <c r="J39" s="45" t="n"/>
     </row>
-    <row r="40"/>
     <row r="41" ht="21.75" customHeight="1" s="29">
       <c r="A41" s="32" t="inlineStr">
         <is>
@@ -2450,7 +2446,6 @@
       <c r="I44" s="45" t="n"/>
       <c r="J44" s="45" t="n"/>
     </row>
-    <row r="45"/>
     <row r="46" ht="21.75" customHeight="1" s="29">
       <c r="A46" s="32" t="inlineStr">
         <is>
